--- a/audio_ficition/utils/publish_log/scifi.xlsx
+++ b/audio_ficition/utils/publish_log/scifi.xlsx
@@ -587,9 +587,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-06-17 11:11:59</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -617,7 +621,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-06-13 14:01:33</t>
+          <t>2025-06-17 23:11:59</t>
         </is>
       </c>
     </row>
@@ -632,7 +636,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-06-13 18:01:33</t>
+          <t>2025-06-18 11:11:59</t>
         </is>
       </c>
     </row>
@@ -647,7 +651,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-06-13 22:01:33</t>
+          <t>2025-06-18 23:11:59</t>
         </is>
       </c>
     </row>
@@ -662,7 +666,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-06-14 02:01:33</t>
+          <t>2025-06-19 11:11:59</t>
         </is>
       </c>
     </row>
@@ -677,7 +681,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-06-14 06:01:33</t>
+          <t>2025-06-19 23:11:59</t>
         </is>
       </c>
     </row>
@@ -688,13 +692,9 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2025-06-14 10:01:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -703,13 +703,9 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2025-06-14 14:01:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -718,13 +714,9 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2025-06-14 18:01:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -733,13 +725,9 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2025-06-14 22:01:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -748,13 +736,9 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2025-06-15 02:01:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/audio_ficition/utils/publish_log/scifi.xlsx
+++ b/audio_ficition/utils/publish_log/scifi.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,11 +454,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025-06-11 22:01:33</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -469,11 +465,7 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2025-06-12 02:01:33</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -484,11 +476,7 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2025-06-12 06:01:33</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -499,11 +487,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2025-06-12 10:01:33</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -514,11 +498,7 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2025-06-12 14:01:33</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -529,11 +509,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2025-06-12 18:01:33</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -544,11 +520,7 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2025-06-12 22:01:33</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,11 +531,7 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2025-06-13 02:01:33</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -574,11 +542,7 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2025-06-13 06:01:33</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -589,11 +553,7 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2025-06-17 11:11:59</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -604,11 +564,7 @@
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2025-06-13 10:01:33</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -619,16 +575,12 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2025-06-17 23:11:59</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14.mp4</t>
+          <t>13.mp4</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -636,158 +588,182 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-06-18 11:11:59</t>
+          <t>2025-07-30 01:27:52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15.mp4</t>
+          <t>14.mp4</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2025-06-18 23:11:59</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16.mp4</t>
+          <t>15.mp4</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2025-06-19 11:11:59</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17.mp4</t>
+          <t>16.mp4</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2025-06-19 23:11:59</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18.mp4</t>
+          <t>17.mp4</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-07-30 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19.mp4</t>
+          <t>18.mp4</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-07-31 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20.mp4</t>
+          <t>19.mp4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-07-31 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21.mp4</t>
+          <t>20.mp4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-08-01 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22.mp4</t>
+          <t>21.mp4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025-08-01 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>23.mp4</t>
+          <t>22.mp4</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-08-02 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24.mp4</t>
+          <t>23.mp4</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-08-02 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25.mp4</t>
+          <t>24.mp4</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-08-03 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26.mp4</t>
+          <t>25.mp4</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-08-03 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27.mp4</t>
+          <t>26.mp4</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -798,7 +774,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>28.mp4</t>
+          <t>27.mp4</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -809,7 +785,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>29.mp4</t>
+          <t>28.mp4</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -820,7 +796,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30.mp4</t>
+          <t>29.mp4</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -831,7 +807,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>31.mp4</t>
+          <t>30.mp4</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -842,7 +818,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>32.mp4</t>
+          <t>31.mp4</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -853,7 +829,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>37.mp4</t>
+          <t>32.mp4</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -864,13 +840,101 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>38.mp4</t>
+          <t>33.mp4</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>35.mp4</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>36.mp4</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>37.mp4</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>39.mp4</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>40.mp4</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>41.mp4</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>42.mp4</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>43.mp4</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/audio_ficition/utils/publish_log/scifi.xlsx
+++ b/audio_ficition/utils/publish_log/scifi.xlsx
@@ -767,9 +767,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2025-08-04 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -778,9 +782,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-08-04 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -789,9 +797,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-08-05 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -800,9 +812,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-08-05 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -811,9 +827,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025-08-06 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -822,9 +842,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2025-08-06 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -833,9 +857,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2025-08-07 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -844,9 +872,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2025-08-07 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -855,9 +887,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2025-08-08 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -866,9 +902,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2025-08-08 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -877,9 +917,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025-08-09 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -888,9 +932,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-08-09 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -899,9 +947,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2025-08-10 01:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -921,9 +973,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2025-08-10 13:27:52</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -932,9 +988,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2025-08-11 01:27:52</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
